--- a/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval.xlsx
@@ -451,10 +451,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6667</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.383</v>
+        <v>0.3958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7391</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4048</v>
+        <v>0.3953</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9528</v>
+        <v>0.9667</v>
       </c>
     </row>
     <row r="4">
@@ -485,13 +485,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7516</v>
+        <v>0.8169</v>
       </c>
     </row>
     <row r="7">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7778</v>
+        <v>0.7368</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -533,10 +533,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5294</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7964</v>
+        <v>0.7922</v>
       </c>
     </row>
     <row r="10">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6667</v>
+        <v>0.7368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2222</v>
+        <v>0.2308</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8</v>
+        <v>0.8667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3529</v>
+        <v>0.3714</v>
       </c>
     </row>
     <row r="3">
@@ -664,16 +664,16 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -689,13 +689,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6667</v>
+        <v>0.8260999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.383</v>
+        <v>0.3958</v>
       </c>
     </row>
     <row r="10">
@@ -877,10 +877,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D2" t="n">
         <v>17</v>
@@ -895,7 +895,7 @@
         <v>17</v>
       </c>
       <c r="H2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -911,19 +911,19 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
@@ -933,25 +933,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>14</v>
       </c>
       <c r="H4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
         <v>17</v>
@@ -976,10 +976,10 @@
         <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -989,25 +989,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -1020,22 +1020,22 @@
         <v>41</v>
       </c>
       <c r="C7" t="n">
+        <v>16</v>
+      </c>
+      <c r="D7" t="n">
         <v>15</v>
       </c>
-      <c r="D7" t="n">
-        <v>16</v>
-      </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -1063,7 +1063,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1077,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.7516</v>
+        <v>0.7913</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Estas peticiones son procesadas y enviadas mediante una conexi´ on interna al servicio functional, que es el que contiene la informaci´ on sensible del sistema. La comunicaci´ on se realiza mediante el protocolo de comunicaci´ on TCP.</t>
+          <t>These requests are processed and sent through an internal connection to the functional service, which is the one that contains the sensitive information of the system. The communication is performed using the TCP communication protocol.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Service responsible for user management, authentication and authorization, and processing requests.</t>
+          <t>Service responsible for the management, authentication and authorization of platform users.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Defines a one-to-many dependency between objects so that when one object changes state, all its dependents are notified.</t>
+          <t>The observer pattern is a software design pattern that defines a one-to-many dependency between objects, so that when one object changes its state, all objects that depend on it are notified and updated automatically.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1385,11 +1385,15 @@
           <t>59</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>['P_03']</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1427,90 +1431,94 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CF_M09_P05</t>
+          <t>CF_M09_AU07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>connector</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8811</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+        <v>0.8425</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Allows sharing information between React components without using props.</t>
+          <t>The client is the user of the platform. [...] The server is the software that is responsible for processing user requests. [...] The communication between both is performed through the internet using the REST API model and the HTTP communication protocol.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>['AU_01', 'AU_02']</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Provider pattern</t>
-        </is>
-      </c>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>client, server</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
+          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU06, CF_M09_AU05</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>CF_M09_P05</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
+          <t>CF_M09_AU07</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>client, waapiti platform</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P_08</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CF_M09_P07</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1519,63 +1527,59 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8833</v>
+        <v>0.9061</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Functions that allow hooking into React state and other features.</t>
+          <t>The platform is a web service that follows the client-server architecture, where the client makes requests to a server that processes them and returns the response.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>P_08</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hook pattern</t>
+          <t>Client-Server Architecture</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
+          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>CF_M09_AU01</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
-          <t>CF_M09_P07</t>
+          <t>CF_M09_P01</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1583,35 +1587,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>pattern</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9061</v>
+        <v>0.9173</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The platform is a web service that follows the client-server architecture.</t>
+          <t>This layer is the core of the application and is responsible for processing all the information.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1623,33 +1627,37 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Client-Server Architecture</t>
+          <t>Business layer (Backend)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>The Waapiti platform is a web service, therefore, as is usual in this type of software, it follows the client-server architecture.</t>
+          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>55</v>
-      </c>
-      <c r="Q7" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>CF_M09_P02</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
-          <t>CF_M09_P01</t>
+          <t>CF_M09_AU19</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1657,12 +1665,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1671,11 +1679,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9173</v>
+        <v>0.989</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1685,7 +1693,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>This layer is the core of the application and is responsible for processing all the information.</t>
+          <t>It is the layer that is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1697,13 +1705,13 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Business layer (Backend)</t>
+          <t>Presentation layer</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1713,11 +1721,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
+          <t>This layer is responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1727,7 +1735,7 @@
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
-          <t>CF_M09_AU19</t>
+          <t>CF_M09_AU08</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1735,12 +1743,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1749,11 +1757,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.989</v>
+        <v>0.9923</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Data Layer</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1763,7 +1771,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for displaying information to the user.</t>
+          <t>It is the layer that is responsible for storing all the data.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1775,13 +1783,13 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_05</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Presentation layer</t>
+          <t>Data layer</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1791,7 +1799,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>This layer is responsible for displaying information to the user.</t>
+          <t>This is the layer responsible for storing information.</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -1805,7 +1813,7 @@
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
-          <t>CF_M09_AU08</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1813,12 +1821,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1827,63 +1835,67 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9923</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>React</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>It is the layer that is responsible for storing all the data.</t>
+          <t>JavaScript library used to build user interfaces.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>['AU_03']</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Data layer</t>
+          <t>React</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>This is the layer responsible for storing information.</t>
+          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
-          <t>CF_M09_AU10</t>
+          <t>CF_M09_AU01</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1891,12 +1903,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1909,7 +1921,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1919,29 +1931,29 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JavaScript library used for building user interfaces in the frontend.</t>
+          <t>Relational database management system used in RDS.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>['AU_03']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1951,21 +1963,21 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Within the software engineering specialization, this project focuses on web technologies, specifically using React [2] and Nest [3] for the codebase and AWS cloud services [4] for the infrastructure.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
-          <t>CF_M09_AU01</t>
+          <t>CF_M09_AU24</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1973,12 +1985,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CF_M09_AU24</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1991,7 +2003,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2001,29 +2013,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Relational database management system used for storing system information.</t>
+          <t>Communication protocol used between client and server.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['AU_16']</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2033,21 +2045,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t xml:space="preserve">Communication between the two is carried out via the internet using the REST API model [30] and the HTTP communication protocol </t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>CF_M09_AU23</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
-          <t>CF_M09_AU24</t>
+          <t>CF_M09_AU40</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -2093,7 +2101,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>['AU_04']</t>
+          <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -2243,7 +2251,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Object storage service used to store multimedia files.</t>
+          <t>AWS object storage service used to store multimedia files.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2320,12 +2328,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frontend architecture based on unidirectional data flow.</t>
+          <t>Flux is a frontend architecture based on the Model-View-Controller (MVC) design pattern, but with the difference that there is no bidirectional communication between the view and the model.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2453,17 +2461,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pattern</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2471,63 +2479,59 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>NoSQL database service used for user cache.</t>
+          <t>This architecture divides the system into three parts, the presentation layer, the business layer and the data layer.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>['AU_05']</t>
+          <t>['P_01']</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>AU_13</t>
+          <t>P_02</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Amazon DynamoDB</t>
+          <t>Three Layers</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>CF_M09_AU10</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
-          <t>CF_M09_AU27</t>
+          <t>CF_M09_P02</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2535,12 +2539,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CF_M09_AU21</t>
+          <t>CF_M09_AU27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2563,39 +2567,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Communication protocol used between business and functional services.</t>
+          <t>AWS NoSQL database service used for user cache.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>['AU_17']</t>
+          <t>['AU_05']</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>AU_15</t>
+          <t>AU_13</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>TCP</t>
+          <t>Amazon DynamoDB</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Communication is carried out using the TCP communication protocol</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -2603,16 +2607,98 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>CF_M09_AU20</t>
+          <t>CF_M09_AU10</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Communication protocol used between business and functional services.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>['AU_17']</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>TCP</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Communication is carried out using the TCP communication protocol</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>CF_M09_AU20</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CF_M09_AU21</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2625,7 +2711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2725,7 +2811,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Service that performs all the important logic of the platform and communicates with the data layer.</t>
+          <t>This is the service that performs all the important logic of the platform.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2745,39 +2831,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>functional service, data layer</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Communication protocol used between client and server.</t>
+          <t>This is the service that performs all the important logic of the platform. It is the service that has communication with the data layer.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>CF_M09_AU19</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Business layer (Backend)</t>
+        </is>
+      </c>
       <c r="H4" t="n">
-        <v>0.7066</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2788,202 +2878,26 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>server, presentation layer</t>
+          <t>business service, amazon dynamodb</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API y el protocolo de comunicaci´ on HTTP.</t>
+          <t>For better response speed of the system, there is a user cache system stored in Amazon DynamoDB, to which the business service has access.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="H5" t="n">
-        <v>0.7314000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>functional service, data layer</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>CF_M09_AU10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Data layer</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>0.7706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>business service, amazon dynamodb</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cache de usuarios: Para mejorar la velocidad de respuesta del sistema, existe un sistema de cach´ e de usuarios almacenada en Amazon DynamoDB, a la cu´ al tiene acceso el servicio business.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>CF_M09_AU26</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>User Cache</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.7848000000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3-Layer Architecture</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>This architecture divides the system into three parts: the presentation layer, the business layer, and the data layer.</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M09_P02</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>0.8511</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MVC</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Model-View-Controller design pattern.</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CF_M09_AU11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>0.7269</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Allows encapsulating information and exposing only what is intended to be shared.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>CF_M09_AU35</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Modules</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9649</v>
+        <v>0.7688</v>
       </c>
     </row>
   </sheetData>
@@ -3066,16 +2980,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.6886</v>
+        <v>0.6791</v>
       </c>
     </row>
     <row r="3">
@@ -3117,43 +3031,43 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
+          <t>CF_M09_AU11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>client, waapiti platform</t>
-        </is>
-      </c>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>This is the part responsible for displaying information to the user.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>P_01</t>
+          <t>P_04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Client-Server</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8557</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M09_AU11</t>
+          <t>CF_M09_AU12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3163,33 +3077,33 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>View</t>
+          <t>Actions</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>This is the part responsible for displaying information to the user.</t>
+          <t>These are the actions that the user can perform.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Observer</t>
+          <t>React</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.7618</v>
+        <v>0.7452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M09_AU12</t>
+          <t>CF_M09_AU13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3199,33 +3113,33 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Actions</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>These are the actions that the user can perform.</t>
+          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.7452</v>
+        <v>0.6807</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M09_AU13</t>
+          <t>CF_M09_AU14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3235,69 +3149,69 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dispatcher</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>It is responsible for storing the application state.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Business Service</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.7081</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M09_AU14</t>
+          <t>CF_M09_AU15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Store</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>actions, store</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>It is responsible for storing the application state.</t>
+          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.6902</v>
+        <v>0.6073</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M09_AU15</t>
+          <t>CF_M09_AU16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3308,240 +3222,240 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>actions, store</t>
+          <t>dispatcher, store</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>They are defined as JavaScript objects and indicate the intention to modify the application's state.</t>
+          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.6199</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M09_AU16</t>
+          <t>CF_M09_AU17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Redux</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>It is responsible for receiving the actions and sending them to the store to modify its state.</t>
+          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
       <c r="H10" t="n">
-        <v>0.6985</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M09_AU17</t>
+          <t>CF_M09_AU18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Layer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>Presentation layer (Backend)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
+          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AU_08</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.7194</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CF_M09_AU18</t>
+          <t>CF_M09_AU22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Presentation layer (Backend)</t>
+          <t>REST</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
+          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.9188</v>
+        <v>0.6758999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CF_M09_AU22</t>
+          <t>CF_M09_AU23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>REST</t>
+          <t>RDS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Defines REST API routes and processes requests to send them to the functional service.</t>
+          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Server</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CF_M09_AU23</t>
+          <t>CF_M09_AU26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RDS</t>
+          <t>User Cache</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+          <t>AU_19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CF_M09_AU26</t>
+          <t>CF_M09_AU28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Component</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>User Cache</t>
+          <t>Typescript</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
+          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
       <c r="H15" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.697</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CF_M09_AU28</t>
+          <t>CF_M09_AU29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3551,33 +3465,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Typescript</t>
+          <t>TypeORM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
+          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.697</v>
+        <v>0.6622</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CF_M09_AU29</t>
+          <t>CF_M09_AU30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3587,33 +3501,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TypeORM</t>
+          <t>Material UI</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
+          <t>is a React library that contains user interface components.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>AU_11</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.6622</v>
+        <v>0.6683</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CF_M09_AU30</t>
+          <t>CF_M09_AU31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3623,33 +3537,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Material UI</t>
+          <t>NextJS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>is a React library that contains user interface components.</t>
+          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>NestJS</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.6683</v>
+        <v>0.7692</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CF_M09_AU31</t>
+          <t>CF_M09_AU32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3659,69 +3573,69 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NextJS</t>
+          <t>Shadcn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
+          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AU_09</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NestJS</t>
+          <t>TCP</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.7692</v>
+        <v>0.6069</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CF_M09_AU32</t>
+          <t>CF_M09_AU33</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shadcn</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
+          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>P_06</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Provider</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.6219</v>
+        <v>0.706</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CF_M09_AU33</t>
+          <t>CF_M09_AU34</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3731,7 +3645,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3742,58 +3656,58 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AU_04</t>
+          <t>AU_03</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Business Layer</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.706</v>
+        <v>0.7635</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CF_M09_AU34</t>
+          <t>CF_M09_AU35</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Modules</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
+          <t>Modules are classes that allow NestJS to organize the application.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AU_03</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Presentation Layer</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.7635</v>
+        <v>0.6216</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CF_M09_AU35</t>
+          <t>CF_M09_AU36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3803,33 +3717,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Modules</t>
+          <t>Controllers</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Modules are classes that allow NestJS to organize the application.</t>
+          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.9649</v>
+        <v>0.6403</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CF_M09_AU36</t>
+          <t>CF_M09_AU37</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3839,173 +3753,173 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Controllers</t>
+          <t>Providers</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Controllers are responsible for receiving and processing HTTP requests.</t>
+          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>P_04</t>
+          <t>AU_06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MVC</t>
+          <t>Business Service</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.7063</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CF_M09_AU37</t>
+          <t>CF_M09_AU38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Providers</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>client, business layer (backend)</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
+          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>P_06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>0.9526</v>
+        <v>0.7089</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
+          <t>CF_M09_AU39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>client, business layer (backend)</t>
-        </is>
-      </c>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Data Layer (Backend)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
+          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AU_17</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>AU_05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Data Layer</t>
+        </is>
+      </c>
       <c r="H26" t="n">
-        <v>0.707</v>
+        <v>0.9248</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF_M09_AU39</t>
+          <t>CF_M09_P05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Layer</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Data Layer (Backend)</t>
+          <t>Provider pattern</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
+          <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AU_05</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Data Layer</t>
+          <t>Functional Service</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.9248</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_M09_P02</t>
+          <t>CF_M09_P06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Architectural Pattern</t>
+          <t>Design Pattern</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Three Layers</t>
+          <t>Module Pattern</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
+          <t>This is the most important pattern in the JavaScript language.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>P_02</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3-Layer Architecture</t>
+          <t>Business Layer</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8511</v>
+        <v>0.6344</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF_M09_P06</t>
+          <t>CF_M09_P07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4015,27 +3929,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Module Pattern</t>
+          <t>Hook pattern</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>This is the most important pattern in the JavaScript language.</t>
+          <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>P_07</t>
+          <t>AU_14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Module</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.6038</v>
       </c>
     </row>
     <row r="30">

--- a/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.3958</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5352</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.3953</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5484</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9667</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.4</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8169</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7913</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_17</t>
@@ -1233,7 +1245,6 @@
           <t>business service, functional service</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M09_AU06, CF_M09_AU19</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M09_AU20</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Business layer</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M09_AU09</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['P_03']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Observer pattern</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M09_P04</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1447,7 +1449,6 @@
       <c r="D5" t="n">
         <v>0.8425</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1468,7 +1469,6 @@
           <t>['AU_01', 'AU_02']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_16</t>
@@ -1479,7 +1479,6 @@
           <t>client, server</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1498,7 +1497,6 @@
           <t>CF_M09_AU06, CF_M09_AU05</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M09_AU07</t>
@@ -1549,14 +1547,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Client-Server Architecture</t>
@@ -1575,14 +1570,11 @@
       <c r="P6" t="n">
         <v>55</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1623,14 +1615,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Business layer (Backend)</t>
@@ -1654,13 +1643,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M09_AU19</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1701,14 +1688,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Presentation layer</t>
@@ -1732,13 +1716,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M09_AU08</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1779,14 +1761,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Data layer</t>
@@ -1810,13 +1789,11 @@
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1862,13 +1839,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>React</t>
@@ -1892,13 +1867,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M09_AU01</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1944,13 +1917,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -1974,13 +1945,11 @@
           <t>CF_M09_AU23</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M09_AU24</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2026,13 +1995,11 @@
           <t>['AU_16']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2051,14 +2018,11 @@
       <c r="P12" t="n">
         <v>55</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M09_AU40</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2104,13 +2068,11 @@
           <t>['AU_06', 'AU_07']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2134,13 +2096,11 @@
           <t>CF_M09_AU33</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M09_AU02</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2181,14 +2141,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2212,13 +2169,11 @@
           <t>CF_M09_P01</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M09_AU06</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2264,13 +2219,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2294,13 +2247,11 @@
           <t>CF_M09_AU39</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M09_AU25</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2346,13 +2297,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Flux</t>
@@ -2376,13 +2325,11 @@
           <t>CF_M09_AU34</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M09_P03</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2423,14 +2370,11 @@
           <t>61</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>AWS</t>
@@ -2449,14 +2393,11 @@
       <c r="P17" t="n">
         <v>9</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M09_AU03</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2502,13 +2443,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2527,14 +2466,11 @@
       <c r="P18" t="n">
         <v>55</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M09_P02</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2580,13 +2516,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2610,13 +2544,11 @@
           <t>CF_M09_AU10</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M09_AU27</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2662,13 +2594,11 @@
           <t>['AU_17']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -2692,13 +2622,11 @@
           <t>CF_M09_AU20</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M09_AU21</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2772,7 +2700,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -2808,7 +2735,6 @@
           <t>Functional Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This is the service that performs all the important logic of the platform.</t>
@@ -2839,7 +2765,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>functional service, data layer</t>
@@ -2875,7 +2800,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>business service, amazon dynamodb</t>
@@ -2972,7 +2896,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player is an external device that allows content to be played on a non professional screen.</t>
@@ -3008,7 +2931,6 @@
           <t>Waapiti Platform</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The main objective of this work is the development of an asset management module that expands the Waapiti software platform and allows us to solve a series of problems and needs of the company.</t>
@@ -3044,7 +2966,6 @@
           <t>View</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>This is the part responsible for displaying information to the user.</t>
@@ -3080,7 +3001,6 @@
           <t>Actions</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>These are the actions that the user can perform.</t>
@@ -3116,7 +3036,6 @@
           <t>Dispatcher</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve"> It is responsible for receiving the actions and sending them to the store to modify its state.</t>
@@ -3152,7 +3071,6 @@
           <t>Store</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>It is responsible for storing the application state.</t>
@@ -3183,7 +3101,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>actions, store</t>
@@ -3219,7 +3136,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>dispatcher, store</t>
@@ -3235,7 +3151,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>0.712</v>
       </c>
@@ -3256,7 +3171,6 @@
           <t>Redux</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Redux is a JavaScript library that allows you to implement the Flux architecture.</t>
@@ -3292,7 +3206,6 @@
           <t>Presentation layer (Backend)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>In this case, the presentation layer is not complex. It corresponds to the user's web browser.</t>
@@ -3328,7 +3241,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Defines REST API routes and processes requests to send them to the functional service.</t>
@@ -3364,7 +3276,6 @@
           <t>RDS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>RDS is a distributed relational database service. In the case of Waapiti, a MySQL database is used and contains all the system information.</t>
@@ -3400,7 +3311,6 @@
           <t>User Cache</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
@@ -3411,7 +3321,6 @@
           <t>AU_19</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>0.7637</v>
       </c>
@@ -3432,7 +3341,6 @@
           <t>Typescript</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>is a superset of JavaScript. It has been used to develop both the backend.</t>
@@ -3468,7 +3376,6 @@
           <t>TypeORM</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>is an ORM (Object Relational Mapping) [41] for TypeScript and JavaScript.</t>
@@ -3504,7 +3411,6 @@
           <t>Material UI</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>is a React library that contains user interface components.</t>
@@ -3540,7 +3446,6 @@
           <t>NextJS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>is a React meta-framework that allows you to easily create web applications (since it provides utilities such as web routing).</t>
@@ -3576,7 +3481,6 @@
           <t>Shadcn</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>is a reusable UI component project that features a modern design and focuses on accessibility and ease of customization of components.</t>
@@ -3612,7 +3516,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -3648,7 +3551,6 @@
           <t>Frontend</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>It should be clear that in this project the author has worked on the entire system, both backend and frontend.</t>
@@ -3684,7 +3586,6 @@
           <t>Modules</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Modules are classes that allow NestJS to organize the application.</t>
@@ -3720,7 +3621,6 @@
           <t>Controllers</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Controllers are responsible for receiving and processing HTTP requests.</t>
@@ -3756,7 +3656,6 @@
           <t>Providers</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Providers are classes that can act as services, repositories, factories, helpers, etc.</t>
@@ -3787,7 +3686,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>client, business layer (backend)</t>
@@ -3803,7 +3701,6 @@
           <t>AU_16</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>0.7089</v>
       </c>
@@ -3824,7 +3721,6 @@
           <t>Data Layer (Backend)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>The data layer is divided into several AWS services that allow for improved system performance and scalability.</t>
@@ -3860,7 +3756,6 @@
           <t>Provider pattern</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>The provider pattern is a software design pattern that allows sharing information between React components without the need to use props.</t>
@@ -3896,7 +3791,6 @@
           <t>Module Pattern</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>This is the most important pattern in the JavaScript language.</t>
@@ -3932,7 +3826,6 @@
           <t>Hook pattern</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>Hooks are a new feature in React that allows you to use state and other React features without writing a class.</t>
@@ -3968,7 +3861,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>TypeORM is an ORM (Object Relational Mapping) that allows you to define database entities as TypeScript classes.</t>
